--- a/data/trans_orig/IP13_R1_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP13_R1_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han tenido que quedar más de la mitad del día en la cama por dolor en 2023 (tasa de respuesta: 99,95%)</t>
+          <t>Menores según si en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>657</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6059</t>
+          <t>5577</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>666</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5735</t>
+          <t>5993</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51452</t>
+          <t>51934</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56856</t>
+          <t>56854</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>113220</t>
+          <t>112962</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>118287</t>
+          <t>118289</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>506</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6403</t>
+          <t>6245</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7441</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2702</t>
+          <t>2530</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>10461</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>152896</t>
+          <t>153054</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>158805</t>
+          <t>158793</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>174389</t>
+          <t>174095</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>180547</t>
+          <t>180443</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>331028</t>
+          <t>330669</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>338428</t>
+          <t>338600</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>470</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5864</t>
+          <t>6295</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10709</t>
+          <t>10460</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>3650</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13160</t>
+          <t>14337</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>167208</t>
+          <t>166777</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>172355</t>
+          <t>172602</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>201781</t>
+          <t>202030</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>210556</t>
+          <t>210474</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>372403</t>
+          <t>371226</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>382128</t>
+          <t>381913</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8506</t>
+          <t>8555</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>879</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9177</t>
+          <t>8384</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3424</t>
+          <t>3650</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13528</t>
+          <t>14110</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>266952</t>
+          <t>266903</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>274220</t>
+          <t>274210</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>296306</t>
+          <t>297099</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>304607</t>
+          <t>304604</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>567412</t>
+          <t>566830</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>577516</t>
+          <t>577290</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5914</t>
+          <t>5973</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16840</t>
+          <t>16943</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,47 +2117,47 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>11864</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>6812</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>19822</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
           <t>0,89%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>11864</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>6848</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>19006</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14731</t>
+          <t>15480</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31003</t>
+          <t>31705</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>648500</t>
+          <t>648397</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>659426</t>
+          <t>659367</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,49 +2230,49 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>99,1%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>749384</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>741426</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>754436</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>98,44%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>97,4%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
           <t>99,11%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>960</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>749384</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>742242</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>754400</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,44%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>97,5%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1886</t>
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1395585</t>
+          <t>1394883</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1411857</t>
+          <t>1411108</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP13_R1_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP13_R1_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2441</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>657</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5577</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,24%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,7%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2170</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>668</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2441</t>
+          <t>2170</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>504</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5993</t>
+          <t>5418</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>55070</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>51934</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>56854</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>95,76%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>90,3%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,86%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>49920</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46762</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>51422</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>116514</t>
+          <t>100457</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>112962</t>
+          <t>97209</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>118289</t>
+          <t>102123</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2786</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>971</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6351</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,05%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2064</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>506</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6245</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3355</t>
-        </is>
-      </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>423</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>6468</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>5419</t>
+          <t>4850</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2530</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10461</t>
+          <t>9968</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>154199</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>150634</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>156014</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,23%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>95,95%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,38%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>255</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>157235</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>153054</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>158793</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>98,7%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,08%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,68%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>178475</t>
+          <t>143454</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>174095</t>
+          <t>139050</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>180443</t>
+          <t>145095</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>335711</t>
+          <t>297653</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>330669</t>
+          <t>292535</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>338600</t>
+          <t>300308</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156985</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156985</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156985</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181830</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181830</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181830</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341130</t>
+          <t>302503</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341130</t>
+          <t>302503</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341130</t>
+          <t>302503</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4973</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1897</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10632</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,48%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,31%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2346</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>470</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6295</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,64%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>2281</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>694</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10460</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>7310</t>
+          <t>7254</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3650</t>
+          <t>3644</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14337</t>
+          <t>13220</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>195153</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>189494</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>198229</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,52%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,69%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,05%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>170726</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>166777</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>172602</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>98,64%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>96,36%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>207526</t>
+          <t>172391</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>202030</t>
+          <t>168565</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>210474</t>
+          <t>173978</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>378253</t>
+          <t>367544</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>371226</t>
+          <t>361578</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>381913</t>
+          <t>371154</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3639</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8705</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>3729</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1248</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8555</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,11%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>4023</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>1372</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8384</t>
+          <t>9259</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>7274</t>
+          <t>7662</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3650</t>
+          <t>3232</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14110</t>
+          <t>14476</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>289006</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>283940</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>291743</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,76%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,03%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,69%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>337</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>271729</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>266903</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>274210</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>98,65%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,89%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>301939</t>
+          <t>252530</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>297099</t>
+          <t>247294</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>304604</t>
+          <t>255181</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>573666</t>
+          <t>541536</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>566830</t>
+          <t>534722</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>577290</t>
+          <t>545966</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>10579</t>
+          <t>11398</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5973</t>
+          <t>6463</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6812</t>
+          <t>6234</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19822</t>
+          <t>17946</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>22443</t>
+          <t>21936</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15480</t>
+          <t>14947</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31705</t>
+          <t>31695</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>688895</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>681246</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>693830</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,37%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,28%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,08%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>926</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>654761</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>648397</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>659367</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>98,41%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,45%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>960</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>749384</t>
+          <t>618295</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>741426</t>
+          <t>610887</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>754436</t>
+          <t>622599</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1404145</t>
+          <t>1307189</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1394883</t>
+          <t>1297430</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1411108</t>
+          <t>1314178</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1426588</t>
+          <t>1329125</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1426588</t>
+          <t>1329125</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1426588</t>
+          <t>1329125</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
